--- a/etf_holdings/2026-09-03_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-03_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-03 01:11:54</t>
+          <t>2026-09-03 21:23:23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,25 +509,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-2.25%2385</t>
+          <t>+0.21%2390</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-2.25%</t>
+          <t>+0.21%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2385</v>
+        <v>2390</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>9.31%11,014,000</t>
+          <t>9.56%11,014,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>9.31%</t>
+          <t>9.56%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-03 01:11:54</t>
+          <t>2026-09-03 21:23:23</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-3.46%5445</t>
+          <t>-2.85%5290</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-3.46%</t>
+          <t>-2.85%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>5445</v>
+        <v>5290</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>9.17%4,750,000</t>
+          <t>9.12%4,750,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>9.17%</t>
+          <t>9.12%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.32%</t>
+          <t>-0.26%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03 01:11:54</t>
+          <t>2026-09-03 21:23:23</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,25 +631,25 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-0.93%4275</t>
+          <t>+1.52%4340</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-0.93%</t>
+          <t>+1.52%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>4275</v>
+        <v>4340</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>7.71%5,088,000</t>
+          <t>8.02%5,088,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>7.71%</t>
+          <t>8.02%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-03 01:11:54</t>
+          <t>2026-09-03 21:23:23</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -687,38 +687,38 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3037欣興</t>
+          <t>3017奇鋐</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+0.21%973</t>
+          <t>-0.3%3300</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+0.21%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>973</v>
+        <v>3300</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>7.00%20,300,000</t>
+          <t>7.13%5,949,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>7.00%</t>
+          <t>7.13%</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>20300000</v>
+        <v>5949000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-03 01:11:54</t>
+          <t>2026-09-03 21:23:23</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -748,38 +748,38 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3017奇鋐</t>
+          <t>3037欣興</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-2.93%3310</t>
+          <t>-5.14%923</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-2.93%</t>
+          <t>-5.14%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>3310</v>
+        <v>923</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6.98%5,949,000</t>
+          <t>6.80%20,300,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>6.98%</t>
+          <t>6.80%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>5949000</v>
+        <v>20300000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>-0.36%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-03 01:11:54</t>
+          <t>2026-09-03 21:23:23</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,25 +814,25 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0%2610</t>
+          <t>-5.17%2475</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-5.17%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2610</v>
+        <v>2475</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>6.00%6,490,561</t>
+          <t>5.83%6,490,561</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>6.00%</t>
+          <t>5.83%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.31%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-03 01:11:54</t>
+          <t>2026-09-03 21:23:23</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,33 +875,33 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-1.95%5770</t>
+          <t>-2.69%5615</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-1.95%</t>
+          <t>-2.69%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>5770</v>
+        <v>5615</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4.90%2,397,000</t>
+          <t>4.95%2,427,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4.90%</t>
+          <t>4.95%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>2397000</v>
+        <v>2427000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-03 01:11:54</t>
+          <t>2026-09-03 21:23:23</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,25 +936,25 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-2.95%2140</t>
+          <t>-2.34%2090</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-2.95%</t>
+          <t>-2.34%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>2140</v>
+        <v>2090</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.90%6,464,000</t>
+          <t>4.91%6,464,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4.90%</t>
+          <t>4.91%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -962,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-03 01:11:54</t>
+          <t>2026-09-03 21:23:23</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,25 +997,25 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-4.93%540</t>
+          <t>-5.37%511</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-4.93%</t>
+          <t>-5.37%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>540</v>
+        <v>511</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.78%24,987,000</t>
+          <t>4.64%24,987,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.78%</t>
+          <t>4.64%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.24%</t>
+          <t>-0.26%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-03 01:11:54</t>
+          <t>2026-09-03 21:23:23</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1053,38 +1053,38 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>6223旺矽</t>
+          <t>2308台達電</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-2.22%5290</t>
+          <t>+1.73%1760</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-2.22%</t>
+          <t>+1.73%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>5290</v>
+        <v>1760</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.64%2,476,000</t>
+          <t>4.63%7,240,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.64%</t>
+          <t>4.63%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>2476000</v>
+        <v>7240000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-03 01:11:54</t>
+          <t>2026-09-03 21:23:23</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1114,38 +1114,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2308台達電</t>
+          <t>6223旺矽</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-7.24%1730</t>
+          <t>-4.63%5045</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-7.24%</t>
+          <t>-4.63%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1730</v>
+        <v>5045</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4.44%7,240,000</t>
+          <t>4.54%2,476,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4.44%</t>
+          <t>4.54%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>7240000</v>
+        <v>2476000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.34%</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-03 01:11:54</t>
+          <t>2026-09-03 21:23:23</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,38 +1175,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>8046南電</t>
+          <t>2303聯電</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-2.04%1200</t>
+          <t>-0.79%125</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-2.04%</t>
+          <t>-0.79%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1200</v>
+        <v>125</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>4.03%9,474,000</t>
+          <t>4.05%89,118,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>4.03%</t>
+          <t>4.05%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>9474000</v>
+        <v>89118000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-03 01:11:54</t>
+          <t>2026-09-03 21:23:23</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,38 +1236,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2303聯電</t>
+          <t>8046南電</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-4.91%126</t>
+          <t>-10%1080</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-4.91%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>126</v>
+        <v>1080</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3.98%89,118,000</t>
+          <t>3.70%9,426,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>3.98%</t>
+          <t>3.70%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>89118000</v>
+        <v>9426000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.20%</t>
+          <t>-0.40%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-03 01:11:54</t>
+          <t>2026-09-03 21:23:23</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1297,38 +1297,38 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>3665貿聯-KY</t>
+          <t>3711日月光投控</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-6.26%2170</t>
+          <t>0%589</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-6.26%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>2170</v>
+        <v>589</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3.53%4,591,848</t>
+          <t>3.60%16,811,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>3.53%</t>
+          <t>3.60%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>4591848</v>
+        <v>16811000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.23%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-03 01:11:54</t>
+          <t>2026-09-03 21:23:23</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,38 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3711日月光投控</t>
+          <t>3665貿聯-KY</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-3.44%589</t>
+          <t>-3.23%2100</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-3.44%</t>
+          <t>-3.23%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>589</v>
+        <v>2100</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3.51%16,811,000</t>
+          <t>3.50%4,591,848</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>3.51%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>16811000</v>
+        <v>4591848</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:06</t>
+          <t>2026-09-03 21:23:35</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,27 +1424,27 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-2.76%1410</t>
+          <t>-4.61%1345</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-2.76%</t>
+          <t>-4.61%</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1410</t>
+          <t>1345</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.70%5,398,000</t>
+          <t>2.64%5,398,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.70%</t>
+          <t>2.64%</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:06</t>
+          <t>2026-09-03 21:23:35</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1487,27 +1487,27 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+3.53%17725</t>
+          <t>+0.71%17850</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>+3.53%</t>
+          <t>+0.71%</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>17725</t>
+          <t>17850</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.31%207,900</t>
+          <t>1.35%207,900</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.31%</t>
+          <t>1.35%</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:06</t>
+          <t>2026-09-03 21:23:35</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1550,27 +1550,27 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-7.66%2110</t>
+          <t>-0.71%2095</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-7.66%</t>
+          <t>-0.71%</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2110</t>
+          <t>2095</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.29%1,731,000</t>
+          <t>1.32%1,731,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>1.32%</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:06</t>
+          <t>2026-09-03 21:23:35</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1613,27 +1613,27 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-3.05%270.5</t>
+          <t>-3.51%261</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-3.05%</t>
+          <t>-3.51%</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>270.5</t>
+          <t>261</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.23%12,818,450</t>
+          <t>1.21%12,818,450</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.23%</t>
+          <t>1.21%</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:06</t>
+          <t>2026-09-03 21:23:35</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1676,27 +1676,27 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-2.22%968</t>
+          <t>-2.07%948</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-2.22%</t>
+          <t>-2.07%</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>968</t>
+          <t>948</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.83%2,427,000</t>
+          <t>0.84%2,427,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.83%</t>
+          <t>0.84%</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:06</t>
+          <t>2026-09-03 21:23:35</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1739,31 +1739,31 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-1.67%5895</t>
+          <t>-1.61%5800</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-1.67%</t>
+          <t>-1.61%</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>5895</t>
+          <t>5800</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.68%325,000</t>
+          <t>0.78%372,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.68%</t>
+          <t>0.78%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>325000</v>
+        <v>372000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:06</t>
+          <t>2026-09-03 21:23:35</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1802,17 +1802,17 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+9.92%3435</t>
+          <t>-2.47%3350</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+9.92%</t>
+          <t>-2.47%</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>3435</t>
+          <t>3350</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:06</t>
+          <t>2026-09-03 21:23:35</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1860,40 +1860,40 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>4979華星光</t>
+          <t>8996高力</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>+4%624</t>
+          <t>-6.32%1185</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+4%</t>
+          <t>-6.32%</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>1185</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.63%2,838,000</t>
+          <t>0.56%1,300,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.63%</t>
+          <t>0.56%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>2838000</v>
+        <v>1300000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:06</t>
+          <t>2026-09-03 21:23:35</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1923,40 +1923,40 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2368金像電</t>
+          <t>4979華星光</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-4.08%1175</t>
+          <t>-8.33%572</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-4.08%</t>
+          <t>-8.33%</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1175</t>
+          <t>572</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.61%1,457,000</t>
+          <t>0.45%2,184,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.61%</t>
+          <t>0.45%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>1457000</v>
+        <v>2184000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:06</t>
+          <t>2026-09-03 21:23:35</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1986,40 +1986,40 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>8996高力</t>
+          <t>3264欣銓</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>+7.66%1265</t>
+          <t>-3.21%226</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>+7.66%</t>
+          <t>-3.21%</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>226</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.58%1,300,000</t>
+          <t>0.41%5,028,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.58%</t>
+          <t>0.41%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>1300000</v>
+        <v>5028000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:06</t>
+          <t>2026-09-03 21:23:35</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2049,40 +2049,40 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>3264欣銓</t>
+          <t>4958臻鼎-KY</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-1.68%233.5</t>
+          <t>-8.48%464</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-1.68%</t>
+          <t>-8.48%</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>233.5</t>
+          <t>464</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.42%5,028,000</t>
+          <t>0.36%2,157,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>0.36%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>5028000</v>
+        <v>2157000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:06</t>
+          <t>2026-09-03 21:23:35</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2112,40 +2112,40 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>4958臻鼎-KY</t>
+          <t>6278台表科</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-5.23%507</t>
+          <t>-4.01%191.5</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-5.23%</t>
+          <t>-4.01%</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>507</t>
+          <t>191.5</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.39%2,157,000</t>
+          <t>0.23%3,248,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.23%</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>2157000</v>
+        <v>3248000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:06</t>
+          <t>2026-09-03 21:23:35</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2175,40 +2175,40 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>6278台表科</t>
+          <t>6271同欣電</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-0.25%199.5</t>
+          <t>-3.36%215.5</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-0.25%</t>
+          <t>-3.36%</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>215.5</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.23%3,248,000</t>
+          <t>0.17%2,222,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.23%</t>
+          <t>0.17%</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>3248000</v>
+        <v>2222000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:06</t>
+          <t>2026-09-03 21:23:35</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2238,40 +2238,40 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>6271同欣電</t>
+          <t>6515穎崴</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-3.46%223</t>
+          <t>-0.71%7000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-3.46%</t>
+          <t>-0.71%</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>7000</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.18%2,222,000</t>
+          <t>0.14%54,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>0.18%</t>
+          <t>0.14%</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>2222000</v>
+        <v>54000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:17</t>
+          <t>2026-09-03 21:23:46</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2306,16 +2306,16 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-2.35%208</t>
+          <t>-1.92%204</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-2.35%</t>
+          <t>-1.92%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:17</t>
+          <t>2026-09-03 21:23:46</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2362,38 +2362,38 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>6515穎崴</t>
+          <t>6191精成科</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+2.03%7050</t>
+          <t>-2.51%81.4</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+2.03%</t>
+          <t>-2.51%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>7050</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.13%54,000</t>
+          <t>0.12%3,988,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.13%</t>
+          <t>0.12%</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>54000</v>
+        <v>3988000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:17</t>
+          <t>2026-09-03 21:23:46</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2423,38 +2423,38 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>6191精成科</t>
+          <t>2368金像電</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-0.95%83.5</t>
+          <t>-6.38%1100</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-0.95%</t>
+          <t>-6.38%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>83.5</v>
+        <v>1100</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.12%3,988,000</t>
+          <t>0.09%219,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.12%</t>
+          <t>0.09%</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>3988000</v>
+        <v>219000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:17</t>
+          <t>2026-09-03 21:23:46</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2484,25 +2484,25 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2313華通</t>
+          <t>2002中鋼</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-1.19%249</t>
+          <t>-0.26%19</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-1.19%</t>
+          <t>-0.26%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>249</v>
+        <v>19</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.04%501,000</t>
+          <t>0.04%5,163,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2511,7 +2511,7 @@
         </is>
       </c>
       <c r="K34" t="n">
-        <v>501000</v>
+        <v>5163000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:17</t>
+          <t>2026-09-03 21:23:46</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2545,38 +2545,38 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2002中鋼</t>
+          <t>2313華通</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0%19.05</t>
+          <t>-5.22%236</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-5.22%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>19.05</v>
+        <v>236</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.03%5,163,000</t>
+          <t>0.04%501,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.03%</t>
+          <t>0.04%</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>5163000</v>
+        <v>501000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:17</t>
+          <t>2026-09-03 21:23:46</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2611,16 +2611,16 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-4.37%503</t>
+          <t>-6.56%470</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-4.37%</t>
+          <t>-6.56%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>503</v>
+        <v>470</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:17</t>
+          <t>2026-09-03 21:23:46</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2672,16 +2672,16 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-1.75%4200</t>
+          <t>0%4050</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-1.75%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>4200</v>
+        <v>4050</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:17</t>
+          <t>2026-09-03 21:23:46</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2733,16 +2733,16 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-0.38%78.3</t>
+          <t>-0.89%77.6</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-0.38%</t>
+          <t>-0.89%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>78.3</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:17</t>
+          <t>2026-09-03 21:23:46</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2794,16 +2794,16 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-3.46%1395</t>
+          <t>-1.43%1375</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-3.46%</t>
+          <t>-1.43%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>1395</v>
+        <v>1375</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:17</t>
+          <t>2026-09-03 21:23:46</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2855,16 +2855,16 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+3.03%7810</t>
+          <t>-8.45%7150</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+3.03%</t>
+          <t>-8.45%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>7810</v>
+        <v>7150</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:17</t>
+          <t>2026-09-03 21:23:46</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2916,16 +2916,16 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-1.46%337</t>
+          <t>-0.59%335</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-1.46%</t>
+          <t>-0.59%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:17</t>
+          <t>2026-09-03 21:23:46</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2977,16 +2977,16 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-2.55%1340</t>
+          <t>-2.99%1300</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-2.55%</t>
+          <t>-2.99%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>1340</v>
+        <v>1300</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:17</t>
+          <t>2026-09-03 21:23:46</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3038,16 +3038,16 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0%518</t>
+          <t>-7.82%477.5</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-7.82%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>518</v>
+        <v>477.5</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:17</t>
+          <t>2026-09-03 21:23:46</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3099,16 +3099,16 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>+0.73%96.3</t>
+          <t>+3.63%99.8</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>+0.73%</t>
+          <t>+3.63%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>96.3</v>
+        <v>99.8</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:17</t>
+          <t>2026-09-03 21:23:46</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3160,16 +3160,16 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-2.71%1975</t>
+          <t>+2.03%2015</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-2.71%</t>
+          <t>+2.03%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>1975</v>
+        <v>2015</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:29</t>
+          <t>2026-09-03 21:23:57</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3221,16 +3221,16 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-2.72%967</t>
+          <t>-4.14%927</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-2.72%</t>
+          <t>-4.14%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>967</v>
+        <v>927</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:29</t>
+          <t>2026-09-03 21:23:57</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3282,16 +3282,16 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-0.17%579</t>
+          <t>-3.63%558</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>-3.63%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>579</v>
+        <v>558</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:29</t>
+          <t>2026-09-03 21:23:57</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3343,16 +3343,16 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-3.22%90.2</t>
+          <t>-1.22%89.1</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-3.22%</t>
+          <t>-1.22%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>90.2</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:29</t>
+          <t>2026-09-03 21:23:57</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3404,16 +3404,16 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-1.95%251</t>
+          <t>-1.39%247.5</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-1.95%</t>
+          <t>-1.39%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>251</v>
+        <v>247.5</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:29</t>
+          <t>2026-09-03 21:23:57</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3465,16 +3465,16 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-2.61%149.5</t>
+          <t>-1.67%147</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-2.61%</t>
+          <t>-1.67%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>149.5</v>
+        <v>147</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-03 01:12:29</t>
+          <t>2026-09-03 21:23:57</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3526,16 +3526,16 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-5.73%148</t>
+          <t>+5.41%156</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-5.73%</t>
+          <t>+5.41%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>

--- a/etf_holdings/2026-09-03_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-03_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-03 21:23:23</t>
+          <t>2026-09-03 21:39:18</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,16 +509,18 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+0.21%2390</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+0.21%</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>2390</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -535,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-03 21:23:23</t>
+          <t>2026-09-03 21:39:18</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,16 +572,18 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-2.85%5290</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-2.85%</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>5290</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -596,7 +600,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03 21:23:23</t>
+          <t>2026-09-03 21:39:18</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,16 +635,18 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+1.52%4340</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+1.52%</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>4340</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -657,7 +663,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-03 21:23:23</t>
+          <t>2026-09-03 21:39:18</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,16 +698,18 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-0.3%3300</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-0.3%</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>3300</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -718,7 +726,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-03 21:23:23</t>
+          <t>2026-09-03 21:39:18</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,16 +761,18 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-5.14%923</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-5.14%</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>923</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -779,7 +789,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.36%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-03 21:23:23</t>
+          <t>2026-09-03 21:39:18</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,16 +824,18 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-5.17%2475</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-5.17%</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>2475</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -840,7 +852,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.31%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-03 21:23:23</t>
+          <t>2026-09-03 21:39:18</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,16 +887,18 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-2.69%5615</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-2.69%</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>5615</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -901,7 +915,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-03 21:23:23</t>
+          <t>2026-09-03 21:39:18</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,16 +950,18 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-2.34%2090</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-2.34%</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>2090</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -962,7 +978,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-03 21:23:23</t>
+          <t>2026-09-03 21:39:18</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,16 +1013,18 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-5.37%511</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-5.37%</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>511</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1023,7 +1041,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-03 21:23:23</t>
+          <t>2026-09-03 21:39:18</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,16 +1076,18 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+1.73%1760</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+1.73%</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>1760</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1084,7 +1104,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-03 21:23:23</t>
+          <t>2026-09-03 21:39:18</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,16 +1139,18 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-4.63%5045</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-4.63%</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>5045</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1145,7 +1167,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-03 21:23:23</t>
+          <t>2026-09-03 21:39:18</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,16 +1202,18 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-0.79%125</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-0.79%</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>125</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1206,7 +1230,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-03 21:23:23</t>
+          <t>2026-09-03 21:39:18</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,16 +1265,18 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-10%1080</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-10%</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>1080</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1267,7 +1293,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.40%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-03 21:23:23</t>
+          <t>2026-09-03 21:39:18</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,16 +1328,18 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0%589</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>589</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1328,7 +1356,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-03 21:23:23</t>
+          <t>2026-09-03 21:39:18</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,16 +1391,18 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-3.23%2100</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-3.23%</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>2100</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1389,7 +1419,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1436,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-03 21:23:35</t>
+          <t>2026-09-03 21:39:25</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1499,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-03 21:23:35</t>
+          <t>2026-09-03 21:39:25</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1562,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-03 21:23:35</t>
+          <t>2026-09-03 21:39:25</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1625,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-03 21:23:35</t>
+          <t>2026-09-03 21:39:25</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1688,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-03 21:23:35</t>
+          <t>2026-09-03 21:39:25</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1751,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-03 21:23:35</t>
+          <t>2026-09-03 21:39:25</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1814,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-03 21:23:35</t>
+          <t>2026-09-03 21:39:25</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1877,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-03 21:23:35</t>
+          <t>2026-09-03 21:39:25</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1940,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-03 21:23:35</t>
+          <t>2026-09-03 21:39:25</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +2003,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-03 21:23:35</t>
+          <t>2026-09-03 21:39:25</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2066,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-03 21:23:35</t>
+          <t>2026-09-03 21:39:25</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2129,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-03 21:23:35</t>
+          <t>2026-09-03 21:39:25</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2192,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-03 21:23:35</t>
+          <t>2026-09-03 21:39:25</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2255,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-03 21:23:35</t>
+          <t>2026-09-03 21:39:25</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2318,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-03 21:23:46</t>
+          <t>2026-09-03 21:39:27</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2379,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-03 21:23:46</t>
+          <t>2026-09-03 21:39:27</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2440,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-03 21:23:46</t>
+          <t>2026-09-03 21:39:27</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2501,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-03 21:23:46</t>
+          <t>2026-09-03 21:39:27</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2562,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-03 21:23:46</t>
+          <t>2026-09-03 21:39:27</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2623,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-03 21:23:46</t>
+          <t>2026-09-03 21:39:27</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2684,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-03 21:23:46</t>
+          <t>2026-09-03 21:39:27</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2745,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-03 21:23:46</t>
+          <t>2026-09-03 21:39:27</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2806,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-03 21:23:46</t>
+          <t>2026-09-03 21:39:27</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2867,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-03 21:23:46</t>
+          <t>2026-09-03 21:39:27</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2928,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-03 21:23:46</t>
+          <t>2026-09-03 21:39:27</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2989,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-03 21:23:46</t>
+          <t>2026-09-03 21:39:27</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3050,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-03 21:23:46</t>
+          <t>2026-09-03 21:39:27</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3111,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-03 21:23:46</t>
+          <t>2026-09-03 21:39:27</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3172,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-03 21:23:46</t>
+          <t>2026-09-03 21:39:27</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3233,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-03 21:23:57</t>
+          <t>2026-09-03 21:39:28</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3294,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-03 21:23:57</t>
+          <t>2026-09-03 21:39:28</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3355,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-03 21:23:57</t>
+          <t>2026-09-03 21:39:28</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3416,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-03 21:23:57</t>
+          <t>2026-09-03 21:39:28</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3477,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-03 21:23:57</t>
+          <t>2026-09-03 21:39:28</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3538,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-03 21:23:57</t>
+          <t>2026-09-03 21:39:28</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-03_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-03_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:18</t>
+          <t>2026-09-03 21:55:17</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,18 +509,16 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+0.21%2390</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+0.21%</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>2390</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -537,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -554,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:18</t>
+          <t>2026-09-03 21:55:17</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -572,18 +570,16 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-2.85%5290</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-2.85%</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>5290</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -600,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.26%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -617,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:18</t>
+          <t>2026-09-03 21:55:17</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -635,18 +631,16 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+1.52%4340</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+1.52%</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>4340</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -663,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -680,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:18</t>
+          <t>2026-09-03 21:55:17</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -698,18 +692,16 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-0.3%3300</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-0.3%</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>3300</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -726,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -743,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:18</t>
+          <t>2026-09-03 21:55:17</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -761,18 +753,16 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-5.14%923</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-5.14%</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>923</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -789,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.36%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -806,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:18</t>
+          <t>2026-09-03 21:55:17</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -824,18 +814,16 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-5.17%2475</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-5.17%</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>2475</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -852,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.31%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -869,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:18</t>
+          <t>2026-09-03 21:55:17</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -887,18 +875,16 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-2.69%5615</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-2.69%</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>5615</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -915,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -932,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:18</t>
+          <t>2026-09-03 21:55:17</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -950,18 +936,16 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-2.34%2090</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-2.34%</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>2090</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -978,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -995,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:18</t>
+          <t>2026-09-03 21:55:17</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1013,18 +997,16 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-5.37%511</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-5.37%</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>511</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1041,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.26%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1058,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:18</t>
+          <t>2026-09-03 21:55:17</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1076,18 +1058,16 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+1.73%1760</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+1.73%</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>1760</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1104,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1121,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:18</t>
+          <t>2026-09-03 21:55:17</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1139,18 +1119,16 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-4.63%5045</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-4.63%</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>5045</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1167,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1184,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:18</t>
+          <t>2026-09-03 21:55:17</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1202,18 +1180,16 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-0.79%125</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-0.79%</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>125</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1230,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1247,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:18</t>
+          <t>2026-09-03 21:55:17</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1265,18 +1241,16 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-10%1080</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-10%</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>1080</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1293,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.40%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1310,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:18</t>
+          <t>2026-09-03 21:55:17</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1328,18 +1302,16 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>0%589</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>589</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1356,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1373,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:18</t>
+          <t>2026-09-03 21:55:17</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1391,18 +1363,16 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-3.23%2100</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-3.23%</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>2100</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1419,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1436,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:25</t>
+          <t>2026-09-03 21:55:22</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1499,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:25</t>
+          <t>2026-09-03 21:55:22</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1562,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:25</t>
+          <t>2026-09-03 21:55:22</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1625,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:25</t>
+          <t>2026-09-03 21:55:22</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1688,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:25</t>
+          <t>2026-09-03 21:55:22</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1751,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:25</t>
+          <t>2026-09-03 21:55:22</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1814,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:25</t>
+          <t>2026-09-03 21:55:22</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1877,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:25</t>
+          <t>2026-09-03 21:55:22</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1940,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:25</t>
+          <t>2026-09-03 21:55:22</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2003,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:25</t>
+          <t>2026-09-03 21:55:22</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2066,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:25</t>
+          <t>2026-09-03 21:55:22</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2129,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:25</t>
+          <t>2026-09-03 21:55:22</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2192,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:25</t>
+          <t>2026-09-03 21:55:22</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2255,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:25</t>
+          <t>2026-09-03 21:55:22</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2318,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:27</t>
+          <t>2026-09-03 21:55:23</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2379,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:27</t>
+          <t>2026-09-03 21:55:23</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2440,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:27</t>
+          <t>2026-09-03 21:55:23</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2501,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:27</t>
+          <t>2026-09-03 21:55:23</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2562,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:27</t>
+          <t>2026-09-03 21:55:23</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2623,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:27</t>
+          <t>2026-09-03 21:55:23</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2684,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:27</t>
+          <t>2026-09-03 21:55:23</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2745,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:27</t>
+          <t>2026-09-03 21:55:23</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2806,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:27</t>
+          <t>2026-09-03 21:55:23</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2867,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:27</t>
+          <t>2026-09-03 21:55:23</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2928,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:27</t>
+          <t>2026-09-03 21:55:23</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2989,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:27</t>
+          <t>2026-09-03 21:55:23</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3050,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:27</t>
+          <t>2026-09-03 21:55:23</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3111,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:27</t>
+          <t>2026-09-03 21:55:23</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3172,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:27</t>
+          <t>2026-09-03 21:55:23</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3233,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:28</t>
+          <t>2026-09-03 21:55:24</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3294,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:28</t>
+          <t>2026-09-03 21:55:24</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3355,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:28</t>
+          <t>2026-09-03 21:55:24</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3416,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:28</t>
+          <t>2026-09-03 21:55:24</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3477,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:28</t>
+          <t>2026-09-03 21:55:24</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3538,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-03 21:39:28</t>
+          <t>2026-09-03 21:55:24</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-03_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-03_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:17</t>
+          <t>2026-09-03 22:30:31</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,16 +509,18 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+0.21%2390</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+0.21%</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>2390</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -535,7 +537,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +554,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:17</t>
+          <t>2026-09-03 22:30:31</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,16 +572,18 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-2.85%5290</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-2.85%</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>5290</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -596,7 +600,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +617,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:17</t>
+          <t>2026-09-03 22:30:31</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,16 +635,18 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+1.52%4340</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+1.52%</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>4340</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -657,7 +663,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +680,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:17</t>
+          <t>2026-09-03 22:30:31</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,16 +698,18 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-0.3%3300</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-0.3%</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>3300</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -718,7 +726,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +743,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:17</t>
+          <t>2026-09-03 22:30:31</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,16 +761,18 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-5.14%923</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-5.14%</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>923</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -779,7 +789,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.36%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +806,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:17</t>
+          <t>2026-09-03 22:30:31</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,16 +824,18 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-5.17%2475</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-5.17%</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>2475</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -840,7 +852,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.31%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +869,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:17</t>
+          <t>2026-09-03 22:30:31</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,16 +887,18 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-2.69%5615</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-2.69%</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>5615</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -901,7 +915,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +932,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:17</t>
+          <t>2026-09-03 22:30:31</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,16 +950,18 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-2.34%2090</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-2.34%</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>2090</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -962,7 +978,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +995,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:17</t>
+          <t>2026-09-03 22:30:31</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,16 +1013,18 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-5.37%511</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-5.37%</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>511</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1023,7 +1041,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1058,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:17</t>
+          <t>2026-09-03 22:30:31</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,16 +1076,18 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+1.73%1760</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+1.73%</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>1760</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1084,7 +1104,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1121,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:17</t>
+          <t>2026-09-03 22:30:31</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,16 +1139,18 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-4.63%5045</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-4.63%</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>5045</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1145,7 +1167,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1184,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:17</t>
+          <t>2026-09-03 22:30:31</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,16 +1202,18 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-0.79%125</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-0.79%</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>125</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1206,7 +1230,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1247,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:17</t>
+          <t>2026-09-03 22:30:31</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,16 +1265,18 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-10%1080</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-10%</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>1080</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1267,7 +1293,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.40%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1310,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:17</t>
+          <t>2026-09-03 22:30:31</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,16 +1328,18 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0%589</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>589</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1328,7 +1356,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1373,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:17</t>
+          <t>2026-09-03 22:30:31</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,16 +1391,18 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-3.23%2100</t>
+          <t>——</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-3.23%</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>2100</v>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1389,7 +1419,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1436,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:22</t>
+          <t>2026-09-03 22:30:36</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1499,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:22</t>
+          <t>2026-09-03 22:30:36</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1562,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:22</t>
+          <t>2026-09-03 22:30:36</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1625,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:22</t>
+          <t>2026-09-03 22:30:36</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1688,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:22</t>
+          <t>2026-09-03 22:30:36</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1751,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:22</t>
+          <t>2026-09-03 22:30:36</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1814,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:22</t>
+          <t>2026-09-03 22:30:36</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1877,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:22</t>
+          <t>2026-09-03 22:30:36</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1940,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:22</t>
+          <t>2026-09-03 22:30:36</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +2003,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:22</t>
+          <t>2026-09-03 22:30:36</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2066,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:22</t>
+          <t>2026-09-03 22:30:36</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2129,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:22</t>
+          <t>2026-09-03 22:30:36</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2192,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:22</t>
+          <t>2026-09-03 22:30:36</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2255,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:22</t>
+          <t>2026-09-03 22:30:36</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2318,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:23</t>
+          <t>2026-09-03 22:30:37</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2379,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:23</t>
+          <t>2026-09-03 22:30:37</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2440,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:23</t>
+          <t>2026-09-03 22:30:37</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2501,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:23</t>
+          <t>2026-09-03 22:30:37</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2562,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:23</t>
+          <t>2026-09-03 22:30:37</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2623,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:23</t>
+          <t>2026-09-03 22:30:37</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2684,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:23</t>
+          <t>2026-09-03 22:30:37</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2745,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:23</t>
+          <t>2026-09-03 22:30:37</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2806,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:23</t>
+          <t>2026-09-03 22:30:37</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2867,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:23</t>
+          <t>2026-09-03 22:30:37</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2928,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:23</t>
+          <t>2026-09-03 22:30:37</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2989,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:23</t>
+          <t>2026-09-03 22:30:37</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3050,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:23</t>
+          <t>2026-09-03 22:30:37</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3111,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:23</t>
+          <t>2026-09-03 22:30:37</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3172,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:23</t>
+          <t>2026-09-03 22:30:37</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3233,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:24</t>
+          <t>2026-09-03 22:30:38</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3294,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:24</t>
+          <t>2026-09-03 22:30:38</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3355,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:24</t>
+          <t>2026-09-03 22:30:38</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3416,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:24</t>
+          <t>2026-09-03 22:30:38</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3477,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:24</t>
+          <t>2026-09-03 22:30:38</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3538,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-03 21:55:24</t>
+          <t>2026-09-03 22:30:38</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-03_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-03_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:31</t>
+          <t>2026-09-03 22:43:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,18 +509,16 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+0.21%2390</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+0.21%</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>2390</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -537,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -554,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:31</t>
+          <t>2026-09-03 22:43:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -572,18 +570,16 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-2.85%5290</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-2.85%</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>5290</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -600,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.26%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -617,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:31</t>
+          <t>2026-09-03 22:43:30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -635,18 +631,16 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+1.52%4340</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+1.52%</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>4340</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -663,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -680,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:31</t>
+          <t>2026-09-03 22:43:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -698,18 +692,16 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-0.3%3300</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-0.3%</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>3300</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -726,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -743,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:31</t>
+          <t>2026-09-03 22:43:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -761,18 +753,16 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-5.14%923</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-5.14%</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>923</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -789,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.36%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -806,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:31</t>
+          <t>2026-09-03 22:43:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -824,18 +814,16 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-5.17%2475</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-5.17%</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>2475</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -852,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.31%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -869,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:31</t>
+          <t>2026-09-03 22:43:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -887,18 +875,16 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-2.69%5615</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-2.69%</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>5615</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -915,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -932,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:31</t>
+          <t>2026-09-03 22:43:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -950,18 +936,16 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-2.34%2090</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-2.34%</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>2090</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -978,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -995,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:31</t>
+          <t>2026-09-03 22:43:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1013,18 +997,16 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-5.37%511</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-5.37%</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>511</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1041,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.26%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1058,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:31</t>
+          <t>2026-09-03 22:43:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1076,18 +1058,16 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>+1.73%1760</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>+1.73%</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>1760</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1104,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1121,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:31</t>
+          <t>2026-09-03 22:43:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1139,18 +1119,16 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-4.63%5045</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-4.63%</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>5045</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1167,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.22%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1184,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:31</t>
+          <t>2026-09-03 22:43:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1202,18 +1180,16 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-0.79%125</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-0.79%</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>125</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1230,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1247,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:31</t>
+          <t>2026-09-03 22:43:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1265,18 +1241,16 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-10%1080</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-10%</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>1080</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1293,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.40%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1310,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:31</t>
+          <t>2026-09-03 22:43:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1328,18 +1302,16 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>0%589</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>589</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1356,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1373,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:31</t>
+          <t>2026-09-03 22:43:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1391,18 +1363,16 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>——</t>
+          <t>-3.23%2100</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>-3.23%</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>2100</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1419,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1436,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:36</t>
+          <t>2026-09-03 22:43:42</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1499,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:36</t>
+          <t>2026-09-03 22:43:42</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1562,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:36</t>
+          <t>2026-09-03 22:43:42</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1625,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:36</t>
+          <t>2026-09-03 22:43:42</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1688,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:36</t>
+          <t>2026-09-03 22:43:42</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1751,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:36</t>
+          <t>2026-09-03 22:43:42</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1814,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:36</t>
+          <t>2026-09-03 22:43:42</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1877,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:36</t>
+          <t>2026-09-03 22:43:42</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1940,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:36</t>
+          <t>2026-09-03 22:43:42</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2003,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:36</t>
+          <t>2026-09-03 22:43:42</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2066,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:36</t>
+          <t>2026-09-03 22:43:42</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2129,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:36</t>
+          <t>2026-09-03 22:43:42</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2192,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:36</t>
+          <t>2026-09-03 22:43:42</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2255,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:36</t>
+          <t>2026-09-03 22:43:42</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2318,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:37</t>
+          <t>2026-09-03 22:43:53</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2379,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:37</t>
+          <t>2026-09-03 22:43:53</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2440,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:37</t>
+          <t>2026-09-03 22:43:53</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2501,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:37</t>
+          <t>2026-09-03 22:43:53</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2562,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:37</t>
+          <t>2026-09-03 22:43:53</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2623,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:37</t>
+          <t>2026-09-03 22:43:53</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2684,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:37</t>
+          <t>2026-09-03 22:43:53</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2745,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:37</t>
+          <t>2026-09-03 22:43:53</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2806,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:37</t>
+          <t>2026-09-03 22:43:53</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2867,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:37</t>
+          <t>2026-09-03 22:43:53</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2928,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:37</t>
+          <t>2026-09-03 22:43:53</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2989,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:37</t>
+          <t>2026-09-03 22:43:53</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3050,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:37</t>
+          <t>2026-09-03 22:43:53</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3111,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:37</t>
+          <t>2026-09-03 22:43:53</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3172,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:37</t>
+          <t>2026-09-03 22:43:53</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3233,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:38</t>
+          <t>2026-09-03 22:44:04</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3294,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:38</t>
+          <t>2026-09-03 22:44:04</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3355,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:38</t>
+          <t>2026-09-03 22:44:04</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3416,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:38</t>
+          <t>2026-09-03 22:44:04</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3477,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:38</t>
+          <t>2026-09-03 22:44:04</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3538,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-03 22:30:38</t>
+          <t>2026-09-03 22:44:04</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-09-03_00981A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-03_00981A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:30</t>
+          <t>2026-09-03 22:59:13</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:30</t>
+          <t>2026-09-03 22:59:13</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:30</t>
+          <t>2026-09-03 22:59:13</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:30</t>
+          <t>2026-09-03 22:59:13</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:30</t>
+          <t>2026-09-03 22:59:13</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:30</t>
+          <t>2026-09-03 22:59:13</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:30</t>
+          <t>2026-09-03 22:59:13</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:30</t>
+          <t>2026-09-03 22:59:13</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:30</t>
+          <t>2026-09-03 22:59:13</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:30</t>
+          <t>2026-09-03 22:59:13</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:30</t>
+          <t>2026-09-03 22:59:13</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:30</t>
+          <t>2026-09-03 22:59:13</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:30</t>
+          <t>2026-09-03 22:59:13</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:30</t>
+          <t>2026-09-03 22:59:13</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:30</t>
+          <t>2026-09-03 22:59:13</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:42</t>
+          <t>2026-09-03 22:59:24</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:42</t>
+          <t>2026-09-03 22:59:24</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:42</t>
+          <t>2026-09-03 22:59:24</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:42</t>
+          <t>2026-09-03 22:59:24</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:42</t>
+          <t>2026-09-03 22:59:24</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:42</t>
+          <t>2026-09-03 22:59:24</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:42</t>
+          <t>2026-09-03 22:59:24</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:42</t>
+          <t>2026-09-03 22:59:24</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:42</t>
+          <t>2026-09-03 22:59:24</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:42</t>
+          <t>2026-09-03 22:59:24</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:42</t>
+          <t>2026-09-03 22:59:24</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:42</t>
+          <t>2026-09-03 22:59:24</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:42</t>
+          <t>2026-09-03 22:59:24</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:42</t>
+          <t>2026-09-03 22:59:24</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:53</t>
+          <t>2026-09-03 22:59:36</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:53</t>
+          <t>2026-09-03 22:59:36</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:53</t>
+          <t>2026-09-03 22:59:36</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:53</t>
+          <t>2026-09-03 22:59:36</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:53</t>
+          <t>2026-09-03 22:59:36</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:53</t>
+          <t>2026-09-03 22:59:36</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:53</t>
+          <t>2026-09-03 22:59:36</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:53</t>
+          <t>2026-09-03 22:59:36</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:53</t>
+          <t>2026-09-03 22:59:36</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:53</t>
+          <t>2026-09-03 22:59:36</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:53</t>
+          <t>2026-09-03 22:59:36</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:53</t>
+          <t>2026-09-03 22:59:36</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3020,7 +3020,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:53</t>
+          <t>2026-09-03 22:59:36</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:53</t>
+          <t>2026-09-03 22:59:36</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-03 22:43:53</t>
+          <t>2026-09-03 22:59:36</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:04</t>
+          <t>2026-09-03 22:59:47</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:04</t>
+          <t>2026-09-03 22:59:47</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:04</t>
+          <t>2026-09-03 22:59:47</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:04</t>
+          <t>2026-09-03 22:59:47</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3447,7 +3447,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:04</t>
+          <t>2026-09-03 22:59:47</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-03 22:44:04</t>
+          <t>2026-09-03 22:59:47</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
